--- a/results_table.xlsx
+++ b/results_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jasper\School\Universiteit\Year_3\Research_Project\Code\anatamae\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CED41F-096B-4FDB-AA81-C47FF8E6F8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDD1BD7-5C5F-463C-AC6E-2FA7EC4B0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="9720" windowWidth="29040" windowHeight="15840" xr2:uid="{B468ABB4-7380-47E3-A26D-E113350E4614}"/>
   </bookViews>
@@ -261,7 +261,6 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -270,6 +269,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -285,6 +285,1142 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="nl-NL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>8px</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="stdErr"/>
+            <c:noEndCap val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:f>Blad1!$C$2:$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>X</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ROI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NONROI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ALL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Blad1!$C$9:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66616610120994069</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.69138670597612806</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69282798193263539</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.71751463885709565</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8AFF-44ED-98EC-441198EC6BB6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>16px</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="stdErr"/>
+            <c:noEndCap val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:f>Blad1!$C$2:$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>X</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ROI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NONROI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ALL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Blad1!$C$19:$F$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66616610120994069</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70457611183780178</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7129923050196203</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.71718826643230638</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8AFF-44ED-98EC-441198EC6BB6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>32px</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="stdErr"/>
+            <c:noEndCap val="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:f>Blad1!$C$2:$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>X</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ROI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NONROI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ALL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Blad1!$C$29:$F$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.66616610120994069</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70323953905057734</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.71441795427294474</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.70465850331098723</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8AFF-44ED-98EC-441198EC6BB6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1009542832"/>
+        <c:axId val="1009547152"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1009542832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1009547152"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1009547152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Average AUC</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1009542832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>173793</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>98740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>471561</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>156189</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Grafiek 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDBA3134-CC7A-038F-403B-432DE276424C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47804DA4-B099-435F-873C-2A0A7839A906}">
-  <dimension ref="B1:O29"/>
+  <dimension ref="B1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
@@ -592,457 +1728,383 @@
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>0.66801345855133998</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>0.68490434924787402</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>0.68250286134728499</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>0.71492422539241296</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>0.66768517004578098</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>0.69941929978744199</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>0.69241794064748197</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>0.71111888897972497</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>0.68335998814584697</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>0.70973164650098097</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>0.68860621729888805</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>0.72113168839927999</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>0.65524852844996695</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>0.67421964417102698</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>0.68334465949967305</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>0.72506540222367499</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>0.65652336085676899</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>0.68865859017331599</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="7">
+      <c r="E7" s="1">
+        <v>0.71726823086984903</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.71533298929038502</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>AVERAGE(C3:C7)</f>
         <v>0.66616610120994069</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f>AVERAGE(D3:D7)</f>
         <v>0.69138670597612806</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>AVERAGE(E3:E7)</f>
-        <v>0.68671791969833207</v>
-      </c>
-      <c r="F9" s="10">
+        <v>0.69282798193263539</v>
+      </c>
+      <c r="F9" s="9">
         <f>AVERAGE(F3:F7)</f>
         <v>0.71751463885709565</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+    <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>0.66801345855133998</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0.71097326684107198</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>0.715354704872465</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>0.72606942854806999</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>0.66768517004578098</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>0.70672212230215803</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>0.70712960881294895</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>0.70232280085022003</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>0.68335998814584697</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>0.71211141881948903</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>0.71700764388489202</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>0.71615051708633004</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>0.65524852844996695</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>0.68482259646827903</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>0.69911911379986902</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>0.71871678793328897</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>0.65652336085676899</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>0.70825115475801104</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>0.72635045372792595</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>0.72268179774362296</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <f>AVERAGE(C13:C17)</f>
         <v>0.66616610120994069</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <f>AVERAGE(D13:D17)</f>
         <v>0.70457611183780178</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <f>AVERAGE(E13:E17)</f>
         <v>0.7129923050196203</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <f>AVERAGE(F13:F17)</f>
         <v>0.71718826643230638</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="10">
         <v>0.66801345855133998</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="10">
         <v>0.70225382194244601</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="10">
         <v>0.71652990107913594</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>0.70927689666448601</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="10">
         <v>0.66768517004578098</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="10">
         <v>0.69674189625572203</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="10">
         <v>0.71303752452583302</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>0.70325529349247795</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="10">
         <v>0.68335998814584697</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="10">
         <v>0.710722898953564</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="10">
         <v>0.71368643721386504</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>0.71110228294637001</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="10">
         <v>0.65524852844996695</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="7"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="6">
+        <v>0.69444898626553297</v>
+      </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="10">
         <v>0.65652336085676899</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="7"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="6">
+        <v>0.70520905718606897</v>
+      </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="8">
         <f>AVERAGE(C23:C27)</f>
         <v>0.66616610120994069</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <f t="shared" ref="D29:F29" si="0">AVERAGE(D23:D27)</f>
         <v>0.70323953905057734</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <f t="shared" si="0"/>
         <v>0.71441795427294474</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="0"/>
-        <v>0.7078781577011114</v>
+        <v>0.70465850331098723</v>
       </c>
     </row>
   </sheetData>
@@ -1060,5 +2122,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/results_table.xlsx
+++ b/results_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jasper\School\Universiteit\Year_3\Research_Project\Code\anatamae\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDD1BD7-5C5F-463C-AC6E-2FA7EC4B0AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA41F2B-94BF-4BF8-AB4E-0AAC98146801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="9720" windowWidth="29040" windowHeight="15840" xr2:uid="{B468ABB4-7380-47E3-A26D-E113350E4614}"/>
   </bookViews>
@@ -25,16 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="13">
-  <si>
-    <t>ROI</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>NONROI</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="34">
   <si>
     <t>Run1:</t>
   </si>
@@ -111,20 +102,395 @@
     </r>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
     <t>Run4:</t>
   </si>
   <si>
     <t>Run5:</t>
+  </si>
+  <si>
+    <t>No masking</t>
+  </si>
+  <si>
+    <t>Full masking</t>
+  </si>
+  <si>
+    <t>Background masking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROI masking </t>
+  </si>
+  <si>
+    <t>Patch size</t>
+  </si>
+  <si>
+    <t>8px</t>
+  </si>
+  <si>
+    <t>16px</t>
+  </si>
+  <si>
+    <t>32px</t>
+  </si>
+  <si>
+    <t>ROI masking</t>
+  </si>
+  <si>
+    <t>Run 1</t>
+  </si>
+  <si>
+    <t>Run 2</t>
+  </si>
+  <si>
+    <t>Run 3</t>
+  </si>
+  <si>
+    <t>Run 4</t>
+  </si>
+  <si>
+    <t>Run 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average </t>
+  </si>
+  <si>
+    <r>
+      <t>0.69138671 ±0.0107</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.5%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.681 – 0.702</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.69282798 ±0.0112</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.6%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.682 – 0.704</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.71751464 ±0.00434</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±0.6%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.713 – 0.722</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.714847582 ±0.0115</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.6%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.703 – 0.726</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.70457611 ±0.00882</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.3%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.696 – 0.713</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.71299231 ±0.00810</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.1%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.705 – 0.721</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.70558231 ±0.00493</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±0.7%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.701 – 0.711</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.7103218 ±0.00453</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±0.6%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.706 – 0.715</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.7046585 ±0.00510</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±0.7%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.700 – 0.710</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0.71718827 ±0.00716</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (±1.0%) [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.710 – 0.724</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,16 +511,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -254,11 +650,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -269,7 +704,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -302,6 +781,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Model</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> performance</a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -333,7 +842,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10052805951984289"/>
+          <c:y val="0.11568580932396536"/>
+          <c:w val="0.87819788495989759"/>
+          <c:h val="0.72749293668757176"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -354,40 +873,22 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:errBars>
-            <c:errBarType val="both"/>
-            <c:errValType val="stdErr"/>
-            <c:noEndCap val="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:errBars>
           <c:cat>
             <c:strRef>
               <c:f>Blad1!$C$2:$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>X</c:v>
+                  <c:v>No masking</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>ROI</c:v>
+                  <c:v>ROI masking</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>NONROI</c:v>
+                  <c:v>Background masking</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>ALL</c:v>
+                  <c:v>Full masking</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -427,7 +928,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent3"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -435,40 +936,22 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:errBars>
-            <c:errBarType val="both"/>
-            <c:errValType val="stdErr"/>
-            <c:noEndCap val="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:errBars>
           <c:cat>
             <c:strRef>
               <c:f>Blad1!$C$2:$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>X</c:v>
+                  <c:v>No masking</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>ROI</c:v>
+                  <c:v>ROI masking</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>NONROI</c:v>
+                  <c:v>Background masking</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>ALL</c:v>
+                  <c:v>Full masking</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -508,7 +991,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent5"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -516,40 +999,22 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:errBars>
-            <c:errBarType val="both"/>
-            <c:errValType val="stdErr"/>
-            <c:noEndCap val="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:errBars>
           <c:cat>
             <c:strRef>
               <c:f>Blad1!$C$2:$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>X</c:v>
+                  <c:v>No masking</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>ROI</c:v>
+                  <c:v>ROI masking</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>NONROI</c:v>
+                  <c:v>Background masking</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>ALL</c:v>
+                  <c:v>Full masking</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -564,10 +1029,10 @@
                   <c:v>0.66616610120994069</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.70323953905057734</c:v>
+                  <c:v>0.70558230972040492</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.71441795427294474</c:v>
+                  <c:v>0.71032179937867845</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.70465850331098723</c:v>
@@ -601,6 +1066,69 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Patch size:</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.31915045412297688"/>
+              <c:y val="0.92799340873711811"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -649,6 +1177,8 @@
         <c:axId val="1009547152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="0.72000000000000008"/>
+          <c:min val="0.64000000000000012"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -666,6 +1196,20 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -687,11 +1231,19 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="nl-NL"/>
-                  <a:t>Average AUC</a:t>
+                  <a:t>Average AUROC (n=5)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.344662562976511E-2"/>
+              <c:y val="0.33132253837514042"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -755,6 +1307,7 @@
         <c:crossAx val="1009542832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="2.0000000000000004E-2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -840,13 +1393,10 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -1386,16 +1936,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>173793</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>98740</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>395067</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152226</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>471561</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>156189</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>340410</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>185370</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1720,27 +2270,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47804DA4-B099-435F-873C-2A0A7839A906}">
-  <dimension ref="B1:F29"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="6" width="22.42578125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="1" customWidth="1"/>
+    <col min="11" max="14" width="18.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="17" max="17" width="45.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="9.140625" style="1"/>
+    <col min="20" max="20" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
@@ -1748,7 +2308,7 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1">
         <v>0.66801345855133998</v>
@@ -1765,7 +2325,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>0.66768517004578098</v>
@@ -1782,7 +2342,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>0.68335998814584697</v>
@@ -1799,7 +2359,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>0.65524852844996695</v>
@@ -1816,7 +2376,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>0.65652336085676899</v>
@@ -1837,7 +2397,7 @@
     </row>
     <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" s="8">
         <f>AVERAGE(C3:C7)</f>
@@ -1859,16 +2419,16 @@
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>10</v>
@@ -1876,7 +2436,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" s="1">
         <v>0.66801345855133998</v>
@@ -1893,7 +2453,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
         <v>0.66768517004578098</v>
@@ -1910,7 +2470,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1">
         <v>0.68335998814584697</v>
@@ -1927,7 +2487,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>0.65524852844996695</v>
@@ -1944,7 +2504,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1">
         <v>0.65652336085676899</v>
@@ -1965,7 +2525,7 @@
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C19" s="8">
         <f>AVERAGE(C13:C17)</f>
@@ -1987,16 +2547,16 @@
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>10</v>
@@ -2004,15 +2564,15 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="10">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
         <v>0.66801345855133998</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="1">
         <v>0.70225382194244601</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="1">
         <v>0.71652990107913594</v>
       </c>
       <c r="F23" s="6">
@@ -2021,15 +2581,15 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="10">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
         <v>0.66768517004578098</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="1">
         <v>0.69674189625572203</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="1">
         <v>0.71303752452583302</v>
       </c>
       <c r="F24" s="6">
@@ -2038,15 +2598,15 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
         <v>0.68335998814584697</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="1">
         <v>0.710722898953564</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="1">
         <v>0.71368643721386504</v>
       </c>
       <c r="F25" s="6">
@@ -2055,40 +2615,45 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="10">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1">
         <v>0.65524852844996695</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="D26" s="1">
+        <v>0.71207692936559797</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.70359891064421198</v>
+      </c>
       <c r="F26" s="6">
         <v>0.69444898626553297</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="10">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
         <v>0.65652336085676899</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="D27" s="1">
+        <v>0.70611600208469505</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.70475622343034605</v>
+      </c>
       <c r="F27" s="6">
         <v>0.70520905718606897</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
       <c r="F28" s="6"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C29" s="8">
         <f>AVERAGE(C23:C27)</f>
@@ -2096,19 +2661,710 @@
       </c>
       <c r="D29" s="8">
         <f t="shared" ref="D29:F29" si="0">AVERAGE(D23:D27)</f>
-        <v>0.70323953905057734</v>
+        <v>0.70558230972040492</v>
       </c>
       <c r="E29" s="8">
         <f t="shared" si="0"/>
-        <v>0.71441795427294474</v>
+        <v>0.71032179937867845</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>0.70465850331098723</v>
       </c>
     </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D35" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E36" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F37" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+    </row>
+    <row r="39" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+      <c r="J39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="O39" s="10"/>
+    </row>
+    <row r="40" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="16">
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="L40" s="16">
+        <v>0.69138670597612806</v>
+      </c>
+      <c r="M40" s="16">
+        <v>0.69282798193263539</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0.71751463885709565</v>
+      </c>
+      <c r="O40" s="10"/>
+    </row>
+    <row r="41" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="16">
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="L41" s="16">
+        <v>0.70457611183780178</v>
+      </c>
+      <c r="M41" s="16">
+        <v>0.7129923050196203</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0.71718826643230638</v>
+      </c>
+      <c r="O41" s="10"/>
+    </row>
+    <row r="42" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="23">
+        <v>0.66801345855133998</v>
+      </c>
+      <c r="D42" s="23">
+        <v>0.68490434924787402</v>
+      </c>
+      <c r="E42" s="23">
+        <v>0.68250286134728499</v>
+      </c>
+      <c r="F42" s="24">
+        <v>0.71492422539241296</v>
+      </c>
+      <c r="G42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" s="17">
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="L42" s="17">
+        <v>0.70558230972040492</v>
+      </c>
+      <c r="M42" s="19">
+        <v>0.71032179937867845</v>
+      </c>
+      <c r="N42" s="18">
+        <v>0.70465850331098723</v>
+      </c>
+      <c r="O42" s="10"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="23">
+        <v>0.66768517004578098</v>
+      </c>
+      <c r="D43" s="23">
+        <v>0.69941929978744199</v>
+      </c>
+      <c r="E43" s="23">
+        <v>0.69241794064748197</v>
+      </c>
+      <c r="F43" s="24">
+        <v>0.71111888897972497</v>
+      </c>
+      <c r="G43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="10"/>
+      <c r="B44" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="23">
+        <v>0.68335998814584697</v>
+      </c>
+      <c r="D44" s="23">
+        <v>0.70973164650098097</v>
+      </c>
+      <c r="E44" s="23">
+        <v>0.68860621729888805</v>
+      </c>
+      <c r="F44" s="24">
+        <v>0.72113168839927999</v>
+      </c>
+      <c r="G44" s="10"/>
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="10"/>
+      <c r="B45" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="23">
+        <v>0.65524852844996695</v>
+      </c>
+      <c r="D45" s="23">
+        <v>0.67421964417102698</v>
+      </c>
+      <c r="E45" s="23">
+        <v>0.68334465949967305</v>
+      </c>
+      <c r="F45" s="24">
+        <v>0.72506540222367499</v>
+      </c>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="10"/>
+      <c r="B46" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="23">
+        <v>0.65652336085676899</v>
+      </c>
+      <c r="D46" s="23">
+        <v>0.68865859017331599</v>
+      </c>
+      <c r="E46" s="23">
+        <v>0.71726823086984903</v>
+      </c>
+      <c r="F46" s="24">
+        <v>0.71533298929038502</v>
+      </c>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="25">
+        <f>AVERAGE(C42:C46)</f>
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="D48" s="25">
+        <f>AVERAGE(D42:D46)</f>
+        <v>0.69138670597612806</v>
+      </c>
+      <c r="E48" s="25">
+        <f>AVERAGE(E42:E46)</f>
+        <v>0.69282798193263539</v>
+      </c>
+      <c r="F48" s="26">
+        <f>AVERAGE(F42:F46)</f>
+        <v>0.71751463885709565</v>
+      </c>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51" s="10"/>
+      <c r="B51" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="J51" s="27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52" s="10"/>
+      <c r="B52" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="23">
+        <v>0.66801345855133998</v>
+      </c>
+      <c r="D52" s="23">
+        <v>0.71097326684107198</v>
+      </c>
+      <c r="E52" s="23">
+        <v>0.715354704872465</v>
+      </c>
+      <c r="F52" s="24">
+        <v>0.72606942854806999</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="J52" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="10"/>
+      <c r="B53" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="23">
+        <v>0.66768517004578098</v>
+      </c>
+      <c r="D53" s="23">
+        <v>0.70672212230215803</v>
+      </c>
+      <c r="E53" s="23">
+        <v>0.70712960881294895</v>
+      </c>
+      <c r="F53" s="24">
+        <v>0.70232280085022003</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="J53" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q53" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="10"/>
+      <c r="B54" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="23">
+        <v>0.68335998814584697</v>
+      </c>
+      <c r="D54" s="23">
+        <v>0.71211141881948903</v>
+      </c>
+      <c r="E54" s="23">
+        <v>0.71700764388489202</v>
+      </c>
+      <c r="F54" s="24">
+        <v>0.71615051708633004</v>
+      </c>
+      <c r="G54" s="10"/>
+      <c r="J54" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q54" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="10"/>
+      <c r="B55" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="23">
+        <v>0.65524852844996695</v>
+      </c>
+      <c r="D55" s="23">
+        <v>0.68482259646827903</v>
+      </c>
+      <c r="E55" s="23">
+        <v>0.69911911379986902</v>
+      </c>
+      <c r="F55" s="24">
+        <v>0.71871678793328897</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="Q55" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="T55" s="1">
+        <v>1.0699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="10"/>
+      <c r="B56" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="23">
+        <v>0.65652336085676899</v>
+      </c>
+      <c r="D56" s="23">
+        <v>0.70825115475801104</v>
+      </c>
+      <c r="E56" s="23">
+        <v>0.72635045372792595</v>
+      </c>
+      <c r="F56" s="24">
+        <v>0.72268179774362296</v>
+      </c>
+      <c r="G56" s="10"/>
+      <c r="T56" s="1">
+        <v>1.12E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="10"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="10"/>
+      <c r="Q57" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="T57" s="1">
+        <v>4.3400000000000001E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10"/>
+      <c r="B58" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="25">
+        <f>AVERAGE(C52:C56)</f>
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="D58" s="25">
+        <f>AVERAGE(D52:D56)</f>
+        <v>0.70457611183780178</v>
+      </c>
+      <c r="E58" s="25">
+        <f>AVERAGE(E52:E56)</f>
+        <v>0.7129923050196203</v>
+      </c>
+      <c r="F58" s="26">
+        <f>AVERAGE(F52:F56)</f>
+        <v>0.71718826643230638</v>
+      </c>
+      <c r="G58" s="10"/>
+      <c r="T58" s="1">
+        <v>1.15E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="10"/>
+      <c r="Q59" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="T59" s="1">
+        <v>8.8199999999999997E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="10"/>
+      <c r="Q60" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="T60" s="1">
+        <v>8.0999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="10"/>
+      <c r="B61" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="Q61" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="T61" s="1">
+        <v>7.1599999999999997E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="10"/>
+      <c r="B62" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="23">
+        <v>0.66801345855133998</v>
+      </c>
+      <c r="D62" s="23">
+        <v>0.70225382194244601</v>
+      </c>
+      <c r="E62" s="23">
+        <v>0.71652990107913594</v>
+      </c>
+      <c r="F62" s="24">
+        <v>0.70927689666448601</v>
+      </c>
+      <c r="G62" s="10"/>
+      <c r="J62" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="T62" s="1">
+        <v>4.9300000000000004E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" s="10"/>
+      <c r="B63" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="23">
+        <v>0.66768517004578098</v>
+      </c>
+      <c r="D63" s="23">
+        <v>0.69674189625572203</v>
+      </c>
+      <c r="E63" s="23">
+        <v>0.71303752452583302</v>
+      </c>
+      <c r="F63" s="24">
+        <v>0.70325529349247795</v>
+      </c>
+      <c r="G63" s="10"/>
+      <c r="J63" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="T63" s="28">
+        <v>4.5300000000000002E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" s="10"/>
+      <c r="B64" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="23">
+        <v>0.68335998814584697</v>
+      </c>
+      <c r="D64" s="23">
+        <v>0.710722898953564</v>
+      </c>
+      <c r="E64" s="23">
+        <v>0.71368643721386504</v>
+      </c>
+      <c r="F64" s="24">
+        <v>0.71110228294637001</v>
+      </c>
+      <c r="G64" s="10"/>
+      <c r="J64" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q64" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="T64" s="1">
+        <v>5.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="10"/>
+      <c r="B65" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="23">
+        <v>0.65524852844996695</v>
+      </c>
+      <c r="D65" s="23">
+        <v>0.71207692936559797</v>
+      </c>
+      <c r="E65" s="23">
+        <v>0.70359891064421198</v>
+      </c>
+      <c r="F65" s="24">
+        <v>0.69444898626553297</v>
+      </c>
+      <c r="G65" s="10"/>
+      <c r="Q65" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="T65" s="1">
+        <f>AVERAGE(T55:T64)</f>
+        <v>7.6380000000000007E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="10"/>
+      <c r="B66" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="23">
+        <v>0.65652336085676899</v>
+      </c>
+      <c r="D66" s="23">
+        <v>0.70611600208469505</v>
+      </c>
+      <c r="E66" s="23">
+        <v>0.70475622343034605</v>
+      </c>
+      <c r="F66" s="24">
+        <v>0.70520905718606897</v>
+      </c>
+      <c r="G66" s="10"/>
+      <c r="Q66" s="27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="10"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="10"/>
+    </row>
+    <row r="68" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="25">
+        <f>AVERAGE(C62:C66)</f>
+        <v>0.66616610120994069</v>
+      </c>
+      <c r="D68" s="25">
+        <f t="shared" ref="D68:F68" si="1">AVERAGE(D62:D66)</f>
+        <v>0.70558230972040492</v>
+      </c>
+      <c r="E68" s="25">
+        <f t="shared" si="1"/>
+        <v>0.71032179937867845</v>
+      </c>
+      <c r="F68" s="26">
+        <f t="shared" si="1"/>
+        <v>0.70465850331098723</v>
+      </c>
+      <c r="G68" s="10"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C9:F9 C19:F19 C29:F29">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C48:F48 C58:F58 C68:F68">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
